--- a/docs/reviews/DBS4_Review_Rows_20260924-5e8a0f10.xlsx
+++ b/docs/reviews/DBS4_Review_Rows_20260924-5e8a0f10.xlsx
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P13" t="n">
         <v>1.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P14" t="n">
         <v>1.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P15" t="n">
         <v>1.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P37" t="n">
         <v>1.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
@@ -3536,13 +3536,13 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P38" t="n">
         <v>1.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
         <v>1.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40">
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P49" t="n">
         <v>1.22</v>
       </c>
       <c r="Q49" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50">
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
         <v>1.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51">
@@ -5195,13 +5195,13 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
         <v>1.22</v>
       </c>
       <c r="Q59" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9460,12 +9460,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9590,12 +9590,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -10170,7 +10170,7 @@
         <v>33</v>
       </c>
       <c r="R123" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S123" t="n">
         <v>0.5</v>
@@ -10179,7 +10179,7 @@
         <v>166</v>
       </c>
       <c r="U123" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10443,7 +10443,7 @@
         <v>33</v>
       </c>
       <c r="R126" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S126" t="n">
         <v>0.5</v>
@@ -10452,7 +10452,7 @@
         <v>166</v>
       </c>
       <c r="U126" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10534,7 +10534,7 @@
         <v>33</v>
       </c>
       <c r="R127" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S127" t="n">
         <v>0.5</v>
@@ -10543,7 +10543,7 @@
         <v>166</v>
       </c>
       <c r="U127" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10898,7 +10898,7 @@
         <v>33</v>
       </c>
       <c r="R131" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S131" t="n">
         <v>0.5</v>
@@ -10907,7 +10907,7 @@
         <v>166</v>
       </c>
       <c r="U131" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -10989,7 +10989,7 @@
         <v>33</v>
       </c>
       <c r="R132" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S132" t="n">
         <v>0.5</v>
@@ -10998,7 +10998,7 @@
         <v>166</v>
       </c>
       <c r="U132" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -11171,7 +11171,7 @@
         <v>33</v>
       </c>
       <c r="R134" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S134" t="n">
         <v>0.5</v>
@@ -11180,7 +11180,7 @@
         <v>166</v>
       </c>
       <c r="U134" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="135">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11899,7 +11899,7 @@
         <v>33</v>
       </c>
       <c r="R142" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S142" t="n">
         <v>0.5</v>
@@ -11908,7 +11908,7 @@
         <v>166</v>
       </c>
       <c r="U142" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="143">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11990,7 +11990,7 @@
         <v>33</v>
       </c>
       <c r="R143" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S143" t="n">
         <v>0.5</v>
@@ -11999,7 +11999,7 @@
         <v>166</v>
       </c>
       <c r="U143" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="144">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -12536,7 +12536,7 @@
         <v>33</v>
       </c>
       <c r="R149" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S149" t="n">
         <v>0.5</v>
@@ -12545,7 +12545,7 @@
         <v>166</v>
       </c>
       <c r="U149" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -13628,7 +13628,7 @@
         <v>33</v>
       </c>
       <c r="R161" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S161" t="n">
         <v>0.5</v>
@@ -13637,7 +13637,7 @@
         <v>166</v>
       </c>
       <c r="U161" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="162">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -13719,7 +13719,7 @@
         <v>33</v>
       </c>
       <c r="R162" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S162" t="n">
         <v>0.5</v>
@@ -13728,7 +13728,7 @@
         <v>166</v>
       </c>
       <c r="U162" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="163">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -15539,7 +15539,7 @@
         <v>33</v>
       </c>
       <c r="R182" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S182" t="n">
         <v>0.5</v>
@@ -15548,7 +15548,7 @@
         <v>166</v>
       </c>
       <c r="U182" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="183">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -15812,7 +15812,7 @@
         <v>33</v>
       </c>
       <c r="R185" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S185" t="n">
         <v>0.5</v>
@@ -15821,7 +15821,7 @@
         <v>166</v>
       </c>
       <c r="U185" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -20817,7 +20817,7 @@
         <v>33</v>
       </c>
       <c r="R240" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S240" t="n">
         <v>0.5</v>
@@ -20826,7 +20826,7 @@
         <v>166</v>
       </c>
       <c r="U240" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="241">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 66 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
+          <t>Due under the push. At today’s pace the planner gives the hero 33 days, but this run pushes Cal King, and at the push pace the run reads about 21 days. Its 120 inbound units have no date and the next PO is 5 November. Source BAMBOO-CALIFKING-WHITE: 49 in FBA, 3 reserved, 120 inbound, 1.62/day, 33 days left. Target BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left. The 15 campaign(s) making this move carry 0.6 ad orders a day, which leaves the target about 61 days of cover. Watch the conversion rate: Olive sells 0.5 a day against White’s 1.6, and the push now ranks on it.</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -21090,7 +21090,7 @@
         <v>33</v>
       </c>
       <c r="R243" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S243" t="n">
         <v>0.5</v>
@@ -21099,7 +21099,7 @@
         <v>166</v>
       </c>
       <c r="U243" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="244">
@@ -23448,12 +23448,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -23513,12 +23513,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -23578,12 +23578,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -23959,12 +23959,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -24103,12 +24103,12 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -24168,12 +24168,12 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>A raise on a campaign the export does not carry: no status, child, or read to check it against. Confirm the campaign and its child first.</t>
+          <t>A raise on a campaign the export’s campaign list does not carry, so no reviewer can recompute it from the export. Command Center carries it as a new campaign: $0 and 0 orders in its first 14 days. A ranking-lane raise to get a new campaign serving is legal inside the band; it stands, flagged.</t>
         </is>
       </c>
     </row>
@@ -34472,10 +34472,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
         <v>30</v>
@@ -34484,7 +34484,7 @@
         <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>48</v>
@@ -34700,7 +34700,7 @@
         <v>1.16</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
@@ -34808,7 +34808,7 @@
         <v>0.41</v>
       </c>
       <c r="H10" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -34958,10 +34958,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
@@ -35012,7 +35012,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -35024,7 +35024,7 @@
         <v>0.34</v>
       </c>
       <c r="H14" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -35120,10 +35120,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>60</v>
@@ -37010,7 +37010,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E51" t="n">
         <v>7</v>
@@ -37022,7 +37022,7 @@
         <v>0.89</v>
       </c>
       <c r="H51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -37226,10 +37226,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
         <v>60</v>
@@ -37496,7 +37496,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E60" t="n">
         <v>8</v>
@@ -37508,7 +37508,7 @@
         <v>0.73</v>
       </c>
       <c r="H60" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
         <v>3</v>
@@ -37616,7 +37616,7 @@
         <v>1.22</v>
       </c>
       <c r="H62" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>17</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>30</v>
@@ -37886,7 +37886,7 @@
         <v>0.58</v>
       </c>
       <c r="H67" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -38877,11 +38877,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BAMBOO-CALIFKING-OLIVE: 76 in FBA, 7 reserved, 30 inbound, 0.50/day, 166 days left</t>
+          <t>BAMBOO-CALIFKING-OLIVE: 70 in FBA, 13 reserved, 30 inbound, 0.50/day, 166 days left</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
@@ -39379,7 +39379,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Re-point by hand to BAMBOO-FULL-OLIVE: 101 in FBA, 3 reserved, 1.22/day, 86 days left.</t>
+          <t>Re-point by hand to BAMBOO-FULL-OLIVE: 100 in FBA, 3 reserved, 1.22/day, 85 days left.</t>
         </is>
       </c>
     </row>
@@ -39455,7 +39455,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Re-point by hand to BAMBOO-CALIFKING-TAUPE: 49 in FBA, 2 reserved, 60 inbound, 2.07/day, 25 days left.</t>
+          <t>Re-point by hand to BAMBOO-CALIFKING-TAUPE: 50 in FBA, 1 reserved, 60 inbound, 2.07/day, 25 days left.</t>
         </is>
       </c>
     </row>

--- a/docs/reviews/DBS4_Review_Rows_20260924-5e8a0f10.xlsx
+++ b/docs/reviews/DBS4_Review_Rows_20260924-5e8a0f10.xlsx
@@ -30366,17 +30366,17 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>after the swap</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Naming only.</t>
+          <t>Stamps BAMBOO-QUEEN-OLIVE, the target of a swap that is due on stock (at risk on the source). Rename once the swap is done by hand, not before.</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -30682,17 +30682,17 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>after the swap</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Naming only.</t>
+          <t>Stamps BAMBOO-QUEEN-OLIVE, the target of a swap that is due on stock (at risk on the source). Rename once the swap is done by hand, not before.</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -31625,22 +31625,22 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Naming only.</t>
+          <t>The name stamps BAMBOO-KING-LIGHTBLUE: 403 in FBA, 51 reserved, 4.13/day, 110 days left, but the ad serves BAMBOO-KING-WHITE: 204 in FBA, 106 reserved, 2430 inbound, 9.81/day, 32 days left, and the swap cannot load (and the swap itself is held on stock). The name would describe a child the campaign does not advertise.</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
